--- a/app/data/walkthrough/Feature Mapping.xlsx
+++ b/app/data/walkthrough/Feature Mapping.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nandini.agrawal_info\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Codes\Danube Properties\Chatbot Initiative Github\Danube-One-Chatbot-Production\app\data\walkthrough\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{361D050B-C737-4FC5-9C36-0C08663D7B8B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F1B0C3D-E454-4474-8FF2-E314AB2782CF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="63">
   <si>
     <t>Feature Name</t>
   </si>
@@ -207,6 +207,9 @@
   </si>
   <si>
     <t>Based on the login if any feature is not authorized.</t>
+  </si>
+  <si>
+    <t>PUBLIC</t>
   </si>
 </sst>
 </file>
@@ -777,7 +780,9 @@
       <c r="A13" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B13" s="5"/>
+      <c r="B13" s="5" t="s">
+        <v>62</v>
+      </c>
       <c r="C13" s="5"/>
       <c r="D13" s="5" t="s">
         <v>32</v>
@@ -858,7 +863,9 @@
       <c r="A18" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B18" s="5"/>
+      <c r="B18" s="5" t="s">
+        <v>62</v>
+      </c>
       <c r="C18" s="5"/>
       <c r="D18" s="5" t="s">
         <v>48</v>
@@ -901,27 +908,39 @@
       <c r="A21" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B21" s="5"/>
+      <c r="B21" s="5" t="s">
+        <v>62</v>
+      </c>
       <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
+      <c r="D21" s="5" t="s">
+        <v>62</v>
+      </c>
       <c r="E21" s="5"/>
     </row>
     <row r="22" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B22" s="5"/>
+      <c r="B22" t="s">
+        <v>62</v>
+      </c>
       <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
+      <c r="D22" t="s">
+        <v>62</v>
+      </c>
       <c r="E22" s="5"/>
     </row>
     <row r="23" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A23" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B23" s="5"/>
+      <c r="B23" t="s">
+        <v>62</v>
+      </c>
       <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
+      <c r="D23" t="s">
+        <v>62</v>
+      </c>
       <c r="E23" s="5"/>
     </row>
     <row r="24" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
